--- a/data/trans_orig/LAWTONBRODY-Edad-trans_orig.xlsx
+++ b/data/trans_orig/LAWTONBRODY-Edad-trans_orig.xlsx
@@ -682,42 +682,42 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>7,14; 7,58</t>
+          <t>7,14; 7,59</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>7,43; 7,74</t>
+          <t>7,44; 7,74</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>7,15; 7,5</t>
+          <t>7,14; 7,5</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>6,92; 7,35</t>
+          <t>6,91; 7,35</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>7,27; 7,55</t>
+          <t>7,24; 7,55</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>7,27; 7,53</t>
+          <t>7,29; 7,54</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>7,11; 7,4</t>
+          <t>7,1; 7,4</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>7,4; 7,62</t>
+          <t>7,41; 7,61</t>
         </is>
       </c>
     </row>
@@ -787,47 +787,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>6,29; 6,86</t>
+          <t>6,28; 6,87</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>5,62; 6,4</t>
+          <t>5,62; 6,39</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6,3; 6,81</t>
+          <t>6,31; 6,83</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6,0; 6,54</t>
+          <t>6,0; 6,52</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>5,18; 5,78</t>
+          <t>5,19; 5,78</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,58; 6,2</t>
+          <t>5,62; 6,23</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,2; 6,6</t>
+          <t>6,17; 6,6</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>5,47; 5,93</t>
+          <t>5,43; 5,95</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>5,94; 6,38</t>
+          <t>5,95; 6,37</t>
         </is>
       </c>
     </row>
@@ -902,22 +902,22 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>6,5; 6,96</t>
+          <t>6,5; 6,94</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>6,98; 7,28</t>
+          <t>6,99; 7,27</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>6,58; 6,93</t>
+          <t>6,58; 6,94</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>6,02; 6,43</t>
+          <t>6,01; 6,43</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -927,17 +927,17 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>6,79; 7,02</t>
+          <t>6,78; 7,03</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>6,29; 6,59</t>
+          <t>6,3; 6,6</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>6,71; 6,96</t>
+          <t>6,7; 6,95</t>
         </is>
       </c>
     </row>
